--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -105,10 +105,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -128,59 +128,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -195,14 +143,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,15 +174,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,6 +203,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -257,7 +250,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,7 +297,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,25 +327,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,49 +357,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,13 +375,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,13 +411,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,13 +435,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,8 +491,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -508,41 +519,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -570,6 +546,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -578,22 +578,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -602,121 +602,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -840,169 +840,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E25" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -105,10 +105,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -126,37 +126,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,25 +134,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -196,10 +151,24 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -217,18 +186,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,11 +225,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,14 +264,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,7 +285,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,7 +297,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,7 +333,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,121 +357,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,13 +387,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,6 +470,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -484,41 +504,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,8 +526,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,8 +550,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -578,145 +578,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -796,19 +796,17 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
+      <sheetName val="StageEvents"/>
+      <sheetName val="Tutorials"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1023,6 +1021,8 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1370,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>56</v>
